--- a/sheets/대금율보/검수/수양산가(首陽山歌).xlsx
+++ b/sheets/대금율보/검수/수양산가(首陽山歌).xlsx
@@ -9542,7 +9542,7 @@
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㒇‹
+          <t xml:space="preserve">㒇
 –
 黃</t>
         </is>
@@ -10333,7 +10333,7 @@
       </c>
       <c r="R12" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃?</t>
+          <t xml:space="preserve">黃</t>
         </is>
       </c>
       <c r="S12" s="26" t="inlineStr">
@@ -10439,8 +10439,7 @@
       </c>
       <c r="R13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">?
-–
+          <t xml:space="preserve">–
 ㄴ
 仲</t>
         </is>
@@ -10562,8 +10561,7 @@
       </c>
       <c r="R14" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">?
-–
+          <t xml:space="preserve">–
 ㄴ</t>
         </is>
       </c>
@@ -10688,7 +10686,7 @@
       </c>
       <c r="R15" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲?
+          <t xml:space="preserve">仲
 –
 ㄴ</t>
         </is>
@@ -10793,11 +10791,7 @@
           <t xml:space="preserve">봉</t>
         </is>
       </c>
-      <c r="R16" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
+      <c r="R16" s="25"/>
       <c r="S16" s="26"/>
       <c r="T16" s="21" t="inlineStr">
         <is>
@@ -10905,11 +10899,7 @@
           <t xml:space="preserve">요</t>
         </is>
       </c>
-      <c r="L19" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
+      <c r="L19" s="25"/>
       <c r="M19" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">목왕</t>
@@ -11020,11 +11010,7 @@
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="L20" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
+      <c r="L20" s="25"/>
       <c r="M20" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
@@ -11127,11 +11113,7 @@
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L21" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
+      <c r="L21" s="25"/>
       <c r="M21" s="26"/>
       <c r="N21" s="21" t="inlineStr">
         <is>
@@ -11239,11 +11221,7 @@
           <t xml:space="preserve">여흔</t>
         </is>
       </c>
-      <c r="L22" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
+      <c r="L22" s="25"/>
       <c r="M22" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">천</t>
@@ -11355,11 +11333,7 @@
           <t xml:space="preserve">락</t>
         </is>
       </c>
-      <c r="L23" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
+      <c r="L23" s="25"/>
       <c r="M23" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
@@ -11465,11 +11439,7 @@
           <t xml:space="preserve">허고</t>
         </is>
       </c>
-      <c r="L24" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
+      <c r="L24" s="25"/>
       <c r="M24" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">로되</t>
@@ -11556,11 +11526,7 @@
       <c r="C27" s="22"/>
       <c r="D27" s="21"/>
       <c r="E27" s="22"/>
-      <c r="F27" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
+      <c r="F27" s="25"/>
       <c r="G27" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">무엇</t>
@@ -11654,11 +11620,7 @@
       <c r="C28" s="22"/>
       <c r="D28" s="21"/>
       <c r="E28" s="22"/>
-      <c r="F28" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
+      <c r="F28" s="25"/>
       <c r="G28" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
@@ -11742,7 +11704,7 @@
       <c r="E29" s="22"/>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃?</t>
+          <t xml:space="preserve">黃</t>
         </is>
       </c>
       <c r="G29" s="26" t="inlineStr">
@@ -11828,11 +11790,7 @@
       <c r="C30" s="22"/>
       <c r="D30" s="21"/>
       <c r="E30" s="22"/>
-      <c r="F30" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
+      <c r="F30" s="25"/>
       <c r="G30" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">허지</t>
@@ -11929,11 +11887,7 @@
       <c r="C31" s="22"/>
       <c r="D31" s="21"/>
       <c r="E31" s="22"/>
-      <c r="F31" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
+      <c r="F31" s="25"/>
       <c r="G31" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">느니</t>
@@ -12027,11 +11981,7 @@
       <c r="C32" s="22"/>
       <c r="D32" s="21"/>
       <c r="E32" s="22"/>
-      <c r="F32" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
+      <c r="F32" s="25"/>
       <c r="G32" s="26"/>
       <c r="H32" s="21" t="inlineStr">
         <is>

--- a/sheets/대금율보/검수/수양산가(首陽山歌).xlsx
+++ b/sheets/대금율보/검수/수양산가(首陽山歌).xlsx
@@ -9368,32 +9368,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="13.46" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="13.46" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="93.02" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="277.43" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="277.43" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="277.43" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
       </c>
       <c r="U5" s="22"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="277.43" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="277.43" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="277.43" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -10100,10 +10100,10 @@
       </c>
       <c r="U8" s="22"/>
     </row>
-    <row r="9">
+    <row r="9" ht="6.0" customHeight="true">
       <c r="A9" s="0"/>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="93.02" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="20" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
       <c r="T10" s="20"/>
       <c r="U10" s="20"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="277.43" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="277.43" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="277.43" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="277.43" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -10583,7 +10583,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="277.43" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="277.43" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -10807,10 +10807,10 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="6.0" customHeight="true">
       <c r="A17" s="0"/>
     </row>
-    <row r="18" ht="60" customHeight="1">
+    <row r="18" ht="93.02" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="20" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
       <c r="T18" s="20"/>
       <c r="U18" s="20"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="277.43" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="277.43" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="277.43" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="277.43" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="277.43" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="277.43" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21" t="inlineStr">
         <is>
@@ -11490,10 +11490,10 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="6.0" customHeight="true">
       <c r="A25" s="0"/>
     </row>
-    <row r="26" ht="60" customHeight="1">
+    <row r="26" ht="93.02" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="20" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
       <c r="T26" s="20"/>
       <c r="U26" s="20"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="277.43" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="22"/>
@@ -11614,7 +11614,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="277.43" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="22"/>
@@ -11696,7 +11696,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="56" customHeight="1">
+    <row r="29" ht="277.43" customHeight="true">
       <c r="A29" s="0"/>
       <c r="B29" s="21"/>
       <c r="C29" s="22"/>
@@ -11784,7 +11784,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="56" customHeight="1">
+    <row r="30" ht="277.43" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="21"/>
       <c r="C30" s="22"/>
@@ -11881,7 +11881,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="56" customHeight="1">
+    <row r="31" ht="277.43" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21"/>
       <c r="C31" s="22"/>
@@ -11975,7 +11975,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="56" customHeight="1">
+    <row r="32" ht="277.43" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21"/>
       <c r="C32" s="22"/>
@@ -12066,7 +12066,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="43"/>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="8" max="16383" man="1"/>
     <brk id="16" max="16383" man="1"/>
